--- a/data/surveyProcessing.xlsx
+++ b/data/surveyProcessing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA875C6-81B4-FB4E-A46B-C4228F732B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FAA9AE-DC72-8F48-9683-16F26C5525D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
+    <workbookView xWindow="1340" yWindow="0" windowWidth="27460" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="222">
   <si>
     <t>Time Started</t>
   </si>
@@ -836,6 +836,9 @@
 Overreported monthly: lshock_hh_inc_bin_annual &gt; income
 No conflict: lshock_hh_inc_bin_annual == income
 NA: no monthly income reported/no annual income reported</t>
+  </si>
+  <si>
+    <t>Used to construct fdi_6m, financial distress index from the first principal component of the 6 adverse financial outcome dummies</t>
   </si>
 </sst>
 </file>
@@ -1048,6 +1051,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1064,57 +1118,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1484,21 +1487,21 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="34" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1514,7 +1517,7 @@
       <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="17"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1530,7 +1533,7 @@
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5" s="17"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1546,7 +1549,7 @@
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="17"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1562,7 +1565,7 @@
       <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1578,7 +1581,7 @@
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="A8" s="17"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1594,7 +1597,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
@@ -1610,7 +1613,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="17"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
@@ -1626,7 +1629,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
@@ -1642,7 +1645,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
@@ -1658,7 +1661,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
@@ -1674,7 +1677,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
@@ -1691,7 +1694,7 @@
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
@@ -1707,7 +1710,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="17"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
@@ -1723,7 +1726,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" ht="170" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
@@ -1739,7 +1742,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A18" s="17"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
@@ -1755,7 +1758,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
@@ -1771,7 +1774,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
@@ -1789,7 +1792,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
@@ -1805,7 +1808,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
@@ -1821,7 +1824,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="36" t="s">
         <v>128</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -1839,7 +1842,7 @@
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1855,7 +1858,7 @@
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="7" t="s">
         <v>23</v>
       </c>
@@ -1871,59 +1874,59 @@
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="38"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="18" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="23"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="19"/>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="24"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="21" t="s">
         <v>129</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -1941,7 +1944,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
@@ -1957,7 +1960,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
@@ -1973,7 +1976,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
@@ -1989,7 +1992,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
+      <c r="A34" s="22"/>
       <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
@@ -2005,7 +2008,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
+      <c r="A35" s="22"/>
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
@@ -2021,7 +2024,7 @@
       <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
@@ -2037,7 +2040,7 @@
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
@@ -2053,7 +2056,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
@@ -2069,7 +2072,7 @@
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
@@ -2087,7 +2090,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
@@ -2103,7 +2106,7 @@
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
@@ -2119,7 +2122,7 @@
       <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A42" s="29"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
@@ -2135,7 +2138,7 @@
       <c r="F42" s="5"/>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
+      <c r="A43" s="22"/>
       <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
@@ -2151,7 +2154,7 @@
       <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
+      <c r="A44" s="22"/>
       <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
@@ -2167,7 +2170,7 @@
       <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
@@ -2183,58 +2186,58 @@
       <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
+      <c r="A46" s="23"/>
       <c r="B46" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="34" t="s">
+      <c r="D46" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="35"/>
+      <c r="E46" s="29"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="18" t="s">
         <v>133</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="18" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
+      <c r="A48" s="19"/>
       <c r="B48" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
     </row>
     <row r="49" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A49" s="24"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
     </row>
     <row r="50" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
@@ -2243,16 +2246,16 @@
       <c r="B50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E50" s="28" t="s">
+      <c r="E50" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="21" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2261,53 +2264,53 @@
       <c r="B51" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="B53" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
     </row>
     <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
       <c r="B54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
     </row>
     <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
     </row>
     <row r="56" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="18" t="s">
         <v>140</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -2325,7 +2328,7 @@
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A57" s="24"/>
+      <c r="A57" s="20"/>
       <c r="B57" s="7" t="s">
         <v>50</v>
       </c>
@@ -2341,7 +2344,7 @@
       <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="21" t="s">
         <v>167</v>
       </c>
       <c r="B58" s="5" t="s">
@@ -2359,7 +2362,7 @@
       <c r="F58" s="5"/>
     </row>
     <row r="59" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+      <c r="A59" s="22"/>
       <c r="B59" s="5" t="s">
         <v>52</v>
       </c>
@@ -2375,7 +2378,7 @@
       <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A60" s="29"/>
+      <c r="A60" s="22"/>
       <c r="B60" s="5" t="s">
         <v>53</v>
       </c>
@@ -2391,7 +2394,7 @@
       <c r="F60" s="5"/>
     </row>
     <row r="61" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
+      <c r="A61" s="23"/>
       <c r="B61" s="5" t="s">
         <v>54</v>
       </c>
@@ -2407,7 +2410,7 @@
       <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="18" t="s">
         <v>168</v>
       </c>
       <c r="B62" s="7" t="s">
@@ -2425,7 +2428,7 @@
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A63" s="24"/>
+      <c r="A63" s="20"/>
       <c r="B63" s="7" t="s">
         <v>56</v>
       </c>
@@ -2441,13 +2444,13 @@
       <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="21" t="s">
         <v>178</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="24" t="s">
         <v>190</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -2456,84 +2459,86 @@
       <c r="E64" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="21" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
+      <c r="A65" s="22"/>
       <c r="B65" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="32"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="5" t="s">
         <v>183</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="22"/>
     </row>
     <row r="66" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
+      <c r="A66" s="22"/>
       <c r="B66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="32"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="22"/>
     </row>
     <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="29"/>
+      <c r="A67" s="22"/>
       <c r="B67" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="32"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="5" t="s">
         <v>185</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="22"/>
     </row>
     <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="29"/>
+      <c r="A68" s="22"/>
       <c r="B68" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="32"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="5" t="s">
         <v>186</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="22"/>
     </row>
     <row r="69" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A69" s="29"/>
+      <c r="A69" s="22"/>
       <c r="B69" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="32"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="23"/>
     </row>
     <row r="70" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A70" s="29"/>
+      <c r="A70" s="22"/>
       <c r="B70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="32"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="5" t="s">
         <v>188</v>
       </c>
@@ -2543,69 +2548,69 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A71" s="29"/>
+      <c r="A71" s="22"/>
       <c r="B71" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="34" t="s">
+      <c r="C71" s="25"/>
+      <c r="D71" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E71" s="36"/>
-      <c r="F71" s="35"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="29"/>
     </row>
     <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A72" s="30"/>
+      <c r="A72" s="23"/>
       <c r="B72" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="34" t="s">
+      <c r="C72" s="26"/>
+      <c r="D72" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="36"/>
-      <c r="F72" s="35"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="29"/>
     </row>
     <row r="73" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="18" t="s">
         <v>197</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C73" s="25" t="s">
+      <c r="C73" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="F73" s="22"/>
+      <c r="F73" s="18"/>
     </row>
     <row r="74" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
+      <c r="A74" s="19"/>
       <c r="B74" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="26"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
     </row>
     <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
+      <c r="A75" s="19"/>
       <c r="B75" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="27"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
     </row>
     <row r="76" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
+      <c r="A76" s="19"/>
       <c r="B76" s="7" t="s">
         <v>69</v>
       </c>
@@ -2621,7 +2626,7 @@
       <c r="F76" s="7"/>
     </row>
     <row r="77" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
+      <c r="A77" s="19"/>
       <c r="B77" s="7" t="s">
         <v>70</v>
       </c>
@@ -2637,7 +2642,7 @@
       <c r="F77" s="7"/>
     </row>
     <row r="78" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A78" s="24"/>
+      <c r="A78" s="20"/>
       <c r="B78" s="7" t="s">
         <v>71</v>
       </c>
@@ -2653,13 +2658,13 @@
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A79" s="28" t="s">
+      <c r="A79" s="21" t="s">
         <v>199</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="24" t="s">
         <v>190</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -2671,11 +2676,11 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A80" s="29"/>
+      <c r="A80" s="22"/>
       <c r="B80" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C80" s="32"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="5" t="s">
         <v>201</v>
       </c>
@@ -2685,11 +2690,11 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A81" s="29"/>
+      <c r="A81" s="22"/>
       <c r="B81" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C81" s="32"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="5" t="s">
         <v>202</v>
       </c>
@@ -2699,11 +2704,11 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="29"/>
+      <c r="A82" s="22"/>
       <c r="B82" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C82" s="32"/>
+      <c r="C82" s="25"/>
       <c r="D82" s="5" t="s">
         <v>203</v>
       </c>
@@ -2713,11 +2718,11 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="29"/>
+      <c r="A83" s="22"/>
       <c r="B83" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C83" s="32"/>
+      <c r="C83" s="25"/>
       <c r="D83" s="5" t="s">
         <v>204</v>
       </c>
@@ -2727,11 +2732,11 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="29"/>
+      <c r="A84" s="22"/>
       <c r="B84" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="32"/>
+      <c r="C84" s="25"/>
       <c r="D84" s="5" t="s">
         <v>205</v>
       </c>
@@ -2741,11 +2746,11 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="29"/>
+      <c r="A85" s="22"/>
       <c r="B85" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C85" s="32"/>
+      <c r="C85" s="25"/>
       <c r="D85" s="5" t="s">
         <v>206</v>
       </c>
@@ -2755,28 +2760,28 @@
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="29"/>
+      <c r="A86" s="22"/>
       <c r="B86" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="32"/>
-      <c r="D86" s="34" t="s">
+      <c r="C86" s="25"/>
+      <c r="D86" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E86" s="36"/>
-      <c r="F86" s="35"/>
+      <c r="E86" s="28"/>
+      <c r="F86" s="29"/>
     </row>
     <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A87" s="30"/>
+      <c r="A87" s="23"/>
       <c r="B87" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C87" s="33"/>
-      <c r="D87" s="34" t="s">
+      <c r="C87" s="26"/>
+      <c r="D87" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="36"/>
-      <c r="F87" s="35"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="29"/>
     </row>
     <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
@@ -2797,7 +2802,7 @@
       <c r="F88" s="7"/>
     </row>
     <row r="89" spans="1:6" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="38" t="s">
+      <c r="A89" s="16" t="s">
         <v>213</v>
       </c>
       <c r="C89" s="15" t="s">
@@ -2811,7 +2816,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A90" s="37"/>
+      <c r="A90" s="17"/>
       <c r="C90" s="3" t="s">
         <v>217</v>
       </c>
@@ -2823,7 +2828,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A91" s="37"/>
+      <c r="A91" s="17"/>
       <c r="C91" s="15" t="s">
         <v>220</v>
       </c>
@@ -2835,14 +2840,21 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="A73:A78"/>
-    <mergeCell ref="A79:A87"/>
-    <mergeCell ref="C79:C87"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
+  <mergeCells count="37">
+    <mergeCell ref="F64:F69"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="E73:E75"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A58:A61"/>
@@ -2859,19 +2871,13 @@
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="E73:E75"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A22"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="A73:A78"/>
+    <mergeCell ref="A79:A87"/>
+    <mergeCell ref="C79:C87"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/surveyProcessing.xlsx
+++ b/data/surveyProcessing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FAA9AE-DC72-8F48-9683-16F26C5525D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF42D3E-5358-164D-B0EB-0F9512866BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1340" yWindow="0" windowWidth="27460" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
   </bookViews>
@@ -535,9 +535,6 @@
     <t>The survey asks respondents to first select an expensi size bin. Then, they report the actual amount. In cases where the reported amount falls within the bin, we use the reported amount. In cases where there is no reported amount or reported amounts are inconsistent with the bin, we use the midpoint of the bin. In cases where no bin is chosen, NA.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Imputed values are denoted with the imputation flag   shock__size_25_imputed</t>
-  </si>
-  <si>
     <t>Predictability and Preventability</t>
   </si>
   <si>
@@ -604,9 +601,6 @@
   </si>
   <si>
     <t>lshock_hh_inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73 people reported a monthly HH income of &gt; 25,0000. 30 of them report an income lower than 25,000 when asked directly. The current imputation rule would assign all these individuals 25,000 as monthly HH income. We have an imputation flag lshock_hh_inc_imputed so we can drop these obs if ever needed. </t>
   </si>
   <si>
     <t>lshock_month</t>
@@ -839,6 +833,13 @@
   </si>
   <si>
     <t>Used to construct fdi_6m, financial distress index from the first principal component of the 6 adverse financial outcome dummies</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Imputed values are denoted with the imputation flag   shock__size_25_imputed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">73 people reported a monthly HH income of &gt; 25,0000. 30 of them report an income lower than 25,000 when asked directly. The current imputation rule would assign all these individuals 25,000 as monthly HH income. We have an imputation flag lshock_hh_inc_imputed so we can drop these obs if ever needed. 
+</t>
   </si>
 </sst>
 </file>
@@ -1051,21 +1052,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1083,15 +1093,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1666,7 +1667,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>11</v>
@@ -1788,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -1834,7 +1835,7 @@
         <v>107</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>91</v>
@@ -1850,7 +1851,7 @@
         <v>119</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>91</v>
@@ -1866,7 +1867,7 @@
         <v>124</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>91</v>
@@ -1896,13 +1897,13 @@
         <v>138</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E27" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="18" t="s">
-        <v>139</v>
+      <c r="F27" s="19" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -1913,7 +1914,7 @@
       <c r="C28" s="35"/>
       <c r="D28" s="36"/>
       <c r="E28" s="36"/>
-      <c r="F28" s="19"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="36"/>
@@ -1923,10 +1924,10 @@
       <c r="C29" s="35"/>
       <c r="D29" s="36"/>
       <c r="E29" s="36"/>
-      <c r="F29" s="20"/>
+      <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="24" t="s">
         <v>129</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -1936,7 +1937,7 @@
         <v>126</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>91</v>
@@ -1944,7 +1945,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>127</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>91</v>
@@ -1960,7 +1961,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>130</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>108</v>
@@ -1976,7 +1977,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
+      <c r="A33" s="25"/>
       <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>130</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>108</v>
@@ -1992,7 +1993,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
+      <c r="A34" s="25"/>
       <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>130</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>108</v>
@@ -2008,7 +2009,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
+      <c r="A35" s="25"/>
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
@@ -2016,7 +2017,7 @@
         <v>130</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>108</v>
@@ -2024,7 +2025,7 @@
       <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>130</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>108</v>
@@ -2040,7 +2041,7 @@
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>130</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>108</v>
@@ -2056,7 +2057,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="22"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>108</v>
@@ -2072,7 +2073,7 @@
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A39" s="22"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
@@ -2080,17 +2081,17 @@
         <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>108</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A40" s="22"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>130</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>108</v>
@@ -2106,7 +2107,7 @@
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
@@ -2114,7 +2115,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>108</v>
@@ -2122,7 +2123,7 @@
       <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A42" s="22"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
@@ -2130,7 +2131,7 @@
         <v>130</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>108</v>
@@ -2138,7 +2139,7 @@
       <c r="F42" s="5"/>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="22"/>
+      <c r="A43" s="25"/>
       <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>130</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>108</v>
@@ -2154,7 +2155,7 @@
       <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A44" s="22"/>
+      <c r="A44" s="25"/>
       <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
@@ -2162,7 +2163,7 @@
         <v>130</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>108</v>
@@ -2170,7 +2171,7 @@
       <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="22"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>130</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>108</v>
@@ -2186,58 +2187,58 @@
       <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="29"/>
+      <c r="E46" s="18"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="19" t="s">
         <v>133</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="18" t="s">
-        <v>161</v>
+      <c r="F47" s="19" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
+      <c r="A48" s="20"/>
       <c r="B48" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="31"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
     </row>
     <row r="49" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C49" s="32"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
@@ -2246,16 +2247,16 @@
       <c r="B50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" s="21" t="s">
+      <c r="D50" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="24" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2264,63 +2265,63 @@
       <c r="B51" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="25"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="B53" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="25"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
     </row>
     <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
       <c r="B54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="25"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
     </row>
     <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
     </row>
     <row r="56" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A56" s="18" t="s">
-        <v>140</v>
+      <c r="A56" s="19" t="s">
+        <v>139</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>91</v>
@@ -2328,15 +2329,15 @@
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A57" s="20"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>108</v>
@@ -2344,17 +2345,17 @@
       <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A58" s="21" t="s">
-        <v>167</v>
+      <c r="A58" s="24" t="s">
+        <v>165</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>91</v>
@@ -2362,15 +2363,15 @@
       <c r="F58" s="5"/>
     </row>
     <row r="59" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A59" s="22"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>91</v>
@@ -2378,15 +2379,15 @@
       <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A60" s="22"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>91</v>
@@ -2394,15 +2395,15 @@
       <c r="F60" s="5"/>
     </row>
     <row r="61" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
+      <c r="A61" s="26"/>
       <c r="B61" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>91</v>
@@ -2410,17 +2411,17 @@
       <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A62" s="18" t="s">
-        <v>168</v>
+      <c r="A62" s="19" t="s">
+        <v>166</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>108</v>
@@ -2428,7 +2429,7 @@
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A63" s="20"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="7" t="s">
         <v>56</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v>95</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>95</v>
@@ -2444,181 +2445,181 @@
       <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
-        <v>178</v>
+      <c r="A64" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C64" s="24" t="s">
-        <v>190</v>
+      <c r="C64" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>221</v>
+        <v>187</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A65" s="22"/>
+      <c r="A65" s="25"/>
       <c r="B65" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="25"/>
+      <c r="C65" s="28"/>
       <c r="D65" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F65" s="22"/>
+        <v>187</v>
+      </c>
+      <c r="F65" s="25"/>
     </row>
     <row r="66" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" s="22"/>
+      <c r="A66" s="25"/>
       <c r="B66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="25"/>
+      <c r="C66" s="28"/>
       <c r="D66" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F66" s="22"/>
+        <v>187</v>
+      </c>
+      <c r="F66" s="25"/>
     </row>
     <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="22"/>
+      <c r="A67" s="25"/>
       <c r="B67" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="25"/>
+      <c r="C67" s="28"/>
       <c r="D67" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F67" s="22"/>
+        <v>187</v>
+      </c>
+      <c r="F67" s="25"/>
     </row>
     <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="22"/>
+      <c r="A68" s="25"/>
       <c r="B68" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="25"/>
+      <c r="C68" s="28"/>
       <c r="D68" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F68" s="22"/>
+        <v>187</v>
+      </c>
+      <c r="F68" s="25"/>
     </row>
     <row r="69" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A69" s="22"/>
+      <c r="A69" s="25"/>
       <c r="B69" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="25"/>
+      <c r="C69" s="28"/>
       <c r="D69" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F69" s="23"/>
+      <c r="F69" s="26"/>
     </row>
     <row r="70" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A70" s="22"/>
+      <c r="A70" s="25"/>
       <c r="B70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="25"/>
+      <c r="C70" s="28"/>
       <c r="D70" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A71" s="22"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="27" t="s">
+      <c r="C71" s="28"/>
+      <c r="D71" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E71" s="28"/>
-      <c r="F71" s="29"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="18"/>
     </row>
     <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A72" s="23"/>
+      <c r="A72" s="26"/>
       <c r="B72" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="26"/>
-      <c r="D72" s="27" t="s">
+      <c r="C72" s="29"/>
+      <c r="D72" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="28"/>
-      <c r="F72" s="29"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="18"/>
     </row>
     <row r="73" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A73" s="18" t="s">
-        <v>197</v>
+      <c r="A73" s="19" t="s">
+        <v>195</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>66</v>
       </c>
       <c r="C73" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E73" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D73" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="F73" s="18"/>
+      <c r="F73" s="19"/>
     </row>
     <row r="74" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
+      <c r="A74" s="20"/>
       <c r="B74" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C74" s="31"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
     </row>
     <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A75" s="19"/>
+      <c r="A75" s="20"/>
       <c r="B75" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C75" s="32"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A76" s="19"/>
+      <c r="A76" s="20"/>
       <c r="B76" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>91</v>
@@ -2626,15 +2627,15 @@
       <c r="F76" s="7"/>
     </row>
     <row r="77" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A77" s="19"/>
+      <c r="A77" s="20"/>
       <c r="B77" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>91</v>
@@ -2642,15 +2643,15 @@
       <c r="F77" s="7"/>
     </row>
     <row r="78" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A78" s="20"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>91</v>
@@ -2658,190 +2659,189 @@
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A79" s="21" t="s">
-        <v>199</v>
+      <c r="A79" s="24" t="s">
+        <v>197</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>190</v>
+      <c r="C79" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A80" s="22"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C80" s="25"/>
+      <c r="C80" s="28"/>
       <c r="D80" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A81" s="22"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C81" s="25"/>
+      <c r="C81" s="28"/>
       <c r="D81" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="22"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C82" s="25"/>
+      <c r="C82" s="28"/>
       <c r="D82" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="22"/>
+      <c r="A83" s="25"/>
       <c r="B83" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C83" s="25"/>
+      <c r="C83" s="28"/>
       <c r="D83" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="22"/>
+      <c r="A84" s="25"/>
       <c r="B84" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="25"/>
+      <c r="C84" s="28"/>
       <c r="D84" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="22"/>
+      <c r="A85" s="25"/>
       <c r="B85" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C85" s="25"/>
+      <c r="C85" s="28"/>
       <c r="D85" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="22"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="25"/>
-      <c r="D86" s="27" t="s">
+      <c r="C86" s="28"/>
+      <c r="D86" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E86" s="28"/>
-      <c r="F86" s="29"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="18"/>
     </row>
     <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A87" s="23"/>
+      <c r="A87" s="26"/>
       <c r="B87" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C87" s="26"/>
-      <c r="D87" s="27" t="s">
+      <c r="C87" s="29"/>
+      <c r="D87" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="28"/>
-      <c r="F87" s="29"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="18"/>
     </row>
     <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F88" s="7"/>
     </row>
     <row r="89" spans="1:6" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="16" t="s">
-        <v>213</v>
+      <c r="A89" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A90" s="17"/>
+      <c r="A90" s="23"/>
       <c r="C90" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E90" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A91" s="23"/>
+      <c r="C91" s="15" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A91" s="17"/>
-      <c r="C91" s="15" t="s">
-        <v>220</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="F64:F69"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:A22"/>
     <mergeCell ref="C27:C29"/>
@@ -2849,12 +2849,6 @@
     <mergeCell ref="E27:E29"/>
     <mergeCell ref="A23:A29"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="E73:E75"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A58:A61"/>
@@ -2868,6 +2862,9 @@
     <mergeCell ref="A30:A46"/>
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="C64:C72"/>
+    <mergeCell ref="F64:F69"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="C47:C49"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D47:D49"/>
@@ -2878,6 +2875,10 @@
     <mergeCell ref="C79:C87"/>
     <mergeCell ref="D86:F86"/>
     <mergeCell ref="D87:F87"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
